--- a/results/Int Task Remove ACC -0.4/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6785500566327726</v>
+        <v>0.6595299479876916</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6723990637142756</v>
+        <v>0.6591717817985798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6860591130633998</v>
+        <v>0.6709708108593743</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6860591130633998</v>
+        <v>0.6718764539221003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6928065148544714</v>
+        <v>0.664816208203249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6932224368456348</v>
+        <v>0.6645362529960822</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6920697272963547</v>
+        <v>0.6692377357158671</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6870393573704425</v>
+        <v>0.679468133236218</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6816668645337663</v>
+        <v>0.6713947544897114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6825147517944407</v>
+        <v>0.6736015074264335</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6823458962898314</v>
+        <v>0.6654791966809666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.68645457987467</v>
+        <v>0.7067384977715887</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6775457474082084</v>
+        <v>0.7164667406796574</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6853632358650696</v>
+        <v>0.7062816654206387</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6866065899370141</v>
+        <v>0.7096988837086926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6789491331816708</v>
+        <v>0.6918234629737179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7032715453206571</v>
+        <v>0.6778469599591859</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7106767215239831</v>
+        <v>0.67432305387012</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7207133964582859</v>
+        <v>0.6722522677173944</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6576729385189487</v>
+        <v>0.6740430986629532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.656330918285166</v>
+        <v>0.6998434978197184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6657258620855619</v>
+        <v>0.7207567133098246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6657258620855619</v>
+        <v>0.722728833300712</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6624819112036631</v>
+        <v>0.7654697311467414</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6622019559964961</v>
+        <v>0.7708013136236311</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6586700282682565</v>
+        <v>0.7618427469942918</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6611940370343037</v>
+        <v>0.7327442508912041</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6356471216754316</v>
+        <v>0.7523234677867014</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6472034961512175</v>
+        <v>0.7480094302390128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6418390249537151</v>
+        <v>0.7407971744578175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6899548221281729</v>
+        <v>0.7446134692947696</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6787610257430444</v>
+        <v>0.7222347003276037</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6825400199578382</v>
+        <v>0.7140502218785396</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6805847454092159</v>
+        <v>0.7217850874519103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6724580227622033</v>
+        <v>0.6681925161315163</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6724580227622033</v>
+        <v>0.6799542445701524</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6463528013168323</v>
+        <v>0.6716506447793568</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6396463098855473</v>
+        <v>0.6996321276274879</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6236924728146649</v>
+        <v>0.6798271015892472</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6377969209740195</v>
+        <v>0.7184007578844691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6283779122561021</v>
+        <v>0.7174044702990787</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6575750745210279</v>
+        <v>0.7171245150919119</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6643144546729256</v>
+        <v>0.7043211768065534</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6676285948975957</v>
+        <v>0.7143730928552864</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6885967586160426</v>
+        <v>0.6979748569741735</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6235565060306684</v>
+        <v>0.6693696916802767</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6188843022938679</v>
+        <v>0.6693696916802767</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6233335044616357</v>
+        <v>0.6693696916802767</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6076640344994657</v>
+        <v>0.6898180531802591</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6136497816509817</v>
+        <v>0.6890110762793713</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5981323217511559</v>
+        <v>0.6984024103421389</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5865430585547573</v>
+        <v>0.6937747267027534</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5824548301498121</v>
+        <v>0.6711873951170678</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5598370163352659</v>
+        <v>0.6738882810268982</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5451842891383797</v>
+        <v>0.6738882810268982</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.52257369479909</v>
+        <v>0.6750951366406017</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5554600089200628</v>
+        <v>0.6829908360794078</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.528107823665119</v>
+        <v>0.6811217941519041</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.522377164639331</v>
+        <v>0.6748641134323952</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5198700013155488</v>
+        <v>0.6667907346858886</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5410507384721024</v>
+        <v>0.6731587129440378</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5060856165592302</v>
+        <v>0.6910686267274599</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5064437827483419</v>
+        <v>0.6650620714439271</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5682773850739755</v>
+        <v>0.62894263565394</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5786561829190424</v>
+        <v>0.6197486339148487</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5786561829190424</v>
+        <v>0.6196704229329038</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5845849764324241</v>
+        <v>0.6106212117809001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.562051790911162</v>
+        <v>0.6062530281687881</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.56185004668594</v>
+        <v>0.6019754890793405</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5623618272652307</v>
+        <v>0.6019754890793405</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5493683761314523</v>
+        <v>0.5187489772410053</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5595097334569735</v>
+        <v>0.5052080492336126</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5070835084724552</v>
+        <v>0.5052080492336126</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.517528885922665</v>
+        <v>0.5004816994323887</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.517528885922665</v>
+        <v>0.5001235332432771</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5380197621102687</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5331121232637162</v>
+        <v>0.4996418338108882</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5397307777460477</v>
+        <v>0.4996418338108882</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5351403947288205</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5378946245391568</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5358852039261111</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5356834597008892</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5669265410371017</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5704015151272072</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4964315738135193</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5010993656487741</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5010211546668293</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5010211546668293</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5006176662163854</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
